--- a/quizzes/038_cyber_security_quiz_for_employees--quizzes.xlsx
+++ b/quizzes/038_cyber_security_quiz_for_employees--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Welcome to the quiz</t>
+          <t>What is the main purpose of a firewall?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_1_title</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Which of the following is a strong password?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the main purpose of a firewall?</t>
+          <t>What is the main difference between two-factor and one-factor authentication?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Which of the following is a strong password</t>
+          <t>What is the purpose of antivirus software?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>When you are working from home, what is the first step you should take to ensure your computer and data is secure?</t>
+          <t>Why is encryption important?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the main purpose of antivirus software?</t>
+          <t>What is the main purpose of a demilitarized zone (DMZ)?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the purpose of a strong password?</t>
+          <t>What is the main purpose of a patch manager?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which of the following is a type of attack that occurs on a network?</t>
+          <t>Why is it important to keep software up-to-date?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the main difference between two-factor and one-factor authentication?</t>
+          <t>What is the main purpose of a secure password manager?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the purpose of a honeypot?</t>
+          <t>What is the difference between phishing and spoofing?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Why is encryption important?</t>
+          <t>What is the main purpose of a honeypot?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,310 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the main purpose of a DMZ (demilitarized zone)?</t>
+          <t>What is the main purpose of a secure network traffic monitor?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a patch manager?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Why is it important to keep software up-to-date?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is the main purpose of a secure password manager?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,136 +827,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>section_1_title_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'section_1',_'value':_'section_1'}</t>
+          <t>8_characters</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Section 1', 'value': 'Section 1'}</t>
+          <t>8 characters</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>section_1_title_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'section_2',_'value':_'section_2'}</t>
+          <t>12_characters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Section 2', 'value': 'Section 2'}</t>
+          <t>12 characters</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'to_filter_spam_emails',_'value':_'filter_spam_emails'}</t>
+          <t>16_characters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'To filter spam emails', 'value': 'filter_spam_emails'}</t>
+          <t>16 characters</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'to_block_malicious_traffic',_'value':_'block_malicious_traffic'}</t>
+          <t>to_detect_and_stop_malware</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'To block malicious traffic', 'value': 'block_malicious_traffic'}</t>
+          <t>To detect and stop malware</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'to_monitor_network_traffic',_'value':_'monitor_network_traffic'}</t>
+          <t>to_monitor_network_traffic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'To monitor network traffic', 'value': 'monitor_network_traffic'}</t>
+          <t>To monitor network traffic</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8_characters',_'value':_'8_characters'}</t>
+          <t>to_update_the_operating_system</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8 characters', 'value': '8_characters'}</t>
+          <t>To update the operating system</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'12_characters',_'value':_'12_characters'}</t>
+          <t>to_monitor_network_traffic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '12 characters', 'value': '12_characters'}</t>
+          <t>To monitor network traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'16_characters',_'value':_'16_characters'}</t>
+          <t>to_block_malicious_traffic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '16 characters', 'value': '16_characters'}</t>
+          <t>To block malicious traffic</t>
         </is>
       </c>
     </row>
@@ -1267,301 +968,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'to_detect_and_stop_malware',_'value':_'detect_and_stop_malware'}</t>
+          <t>to_separate_internal_and_external_networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'To detect and stop malware', 'value': 'detect_and_stop_malware'}</t>
+          <t>To separate internal and external networks</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'to_monitor_network_traffic',_'value':_'monitor_network_traffic'}</t>
+          <t>to_monitor_network_traffic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'To monitor network traffic', 'value': 'monitor_network_traffic'}</t>
+          <t>To monitor network traffic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'to_update_the_operating_system',_'value':_'update_operating_system'}</t>
+          <t>to_detect_and_respond_to_threats</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'To update the operating system', 'value': 'update_operating_system'}</t>
+          <t>To detect and respond to threats</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8_characters',_'value':_'8_characters'}</t>
+          <t>to_prevent_unauthorized_access</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8 characters', 'value': '8_characters'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'12_characters',_'value':_'12_characters'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': '12 characters', 'value': '12_characters'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'16_characters',_'value':_'16_characters'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': '16 characters', 'value': '16_characters'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'phishing',_'value':_'phising'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Phishing', 'value': 'phising'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'spoofing',_'value':_'spoofing'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Spoofing', 'value': 'spoofing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'sniffing',_'value':_'sniffing'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Sniffing', 'value': 'sniffing'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'to_monitor_network_traffic',_'value':_'monitor_network_traffic'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'To monitor network traffic', 'value': 'monitor_network_traffic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'to_detect_and_respond_to_threats',_'value':_'detect_and_respond_to_threats'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'To detect and respond to threats', 'value': 'detect_and_respond_to_threats'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'to_prevent_unauthorized_access',_'value':_'prevent_unauthorized_access'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'To prevent unauthorized access', 'value': 'prevent_unauthorized_access'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'to_monitor_network_traffic',_'value':_'monitor_network_traffic'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'To monitor network traffic', 'value': 'monitor_network_traffic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'to_block_malicious_traffic',_'value':_'block_malicious_traffic'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'To block malicious traffic', 'value': 'block_malicious_traffic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'to_separate_the_internal_and_external_networks',_'value':_'separate_internal_and_external_networks'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'To separate the internal and external networks', 'value': 'separate_internal_and_external_networks'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'to_store_sensitive_information_securely',_'value':_'store_sensitive_info_securely'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'To store sensitive information securely', 'value': 'store_sensitive_info_securely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'to_monitor_network_traffic',_'value':_'monitor_network_traffic'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'To monitor network traffic', 'value': 'monitor_network_traffic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'to_prevent_unauthorized_access',_'value':_'prevent_unauthorized_access'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'To prevent unauthorized access', 'value': 'prevent_unauthorized_access'}</t>
+          <t>To prevent unauthorized access</t>
         </is>
       </c>
     </row>
